--- a/output/pdf_financials_xlsx/AGA.xlsx
+++ b/output/pdf_financials_xlsx/AGA.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4.519965</v>
+        <v>-4.519965</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>10.130666</v>
+        <v>-10.130666</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>4.519965</v>
+        <v>-4.519965</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>10.130666</v>
+        <v>-10.130666</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>4.519965</v>
+        <v>-4.519965</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>10.130666</v>
+        <v>-10.130666</v>
       </c>
     </row>
     <row r="24">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>41.090591</v>
+        <v>-41.090591</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>56.281478</v>
+        <v>-56.281478</v>
       </c>
     </row>
     <row r="27">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>4.519965</v>
+        <v>-4.519965</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>10.130666</v>
+        <v>-10.130666</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>4.519965</v>
+        <v>-4.519965</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10.130666</v>
+        <v>-10.130666</v>
       </c>
     </row>
     <row r="30">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.044848</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.049543</v>
       </c>
     </row>
     <row r="92">
@@ -2730,7 +2730,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.044848</v>
       </c>
@@ -3748,10 +3752,10 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>4.519965</v>
+        <v>-4.519965</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>10.130666</v>
+        <v>-10.130666</v>
       </c>
     </row>
     <row r="60">

--- a/output/pdf_financials_xlsx/AGA.xlsx
+++ b/output/pdf_financials_xlsx/AGA.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.060274</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09245399999999999</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.519965</v>
+        <v>-4.459691</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-10.130666</v>
+        <v>-10.038212</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.519965</v>
+        <v>-4.459691</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-10.130666</v>
+        <v>-10.038212</v>
       </c>
     </row>
     <row r="30">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">

--- a/output/pdf_financials_xlsx/AGA.xlsx
+++ b/output/pdf_financials_xlsx/AGA.xlsx
@@ -3250,7 +3250,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
